--- a/data/performance/daily/signal_list_2026-06-22.xlsx
+++ b/data/performance/daily/signal_list_2026-06-22.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-06-22.xlsx
+++ b/data/performance/daily/signal_list_2026-06-22.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -461,9 +461,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,7 +494,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -518,15 +519,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -563,12 +569,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -605,12 +616,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,12 +663,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -689,12 +710,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -726,17 +752,22 @@
       <c r="G9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -773,12 +804,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -815,12 +851,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -857,12 +898,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -899,12 +945,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -936,17 +987,22 @@
       <c r="G14" s="4" t="n">
         <v>-4.95</v>
       </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -983,12 +1039,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1020,17 +1081,22 @@
       <c r="G16" s="4" t="n">
         <v>-0.87</v>
       </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1047,7 +1113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J116"/>
+  <dimension ref="A1:K116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1057,9 +1123,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1089,7 +1156,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1114,15 +1181,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1154,17 +1226,22 @@
       <c r="G5" s="4" t="n">
         <v>-4.95</v>
       </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1196,17 +1273,22 @@
       <c r="G6" s="4" t="n">
         <v>-2.52</v>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1238,17 +1320,22 @@
       <c r="G7" s="4" t="n">
         <v>-1.82</v>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1280,17 +1367,22 @@
       <c r="G8" s="4" t="n">
         <v>-1.59</v>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1322,17 +1414,22 @@
       <c r="G9" s="4" t="n">
         <v>-4.14</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1364,17 +1461,22 @@
       <c r="G10" s="4" t="n">
         <v>-0.3</v>
       </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1406,17 +1508,22 @@
       <c r="G11" s="4" t="n">
         <v>-5.1</v>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1448,17 +1555,22 @@
       <c r="G12" s="4" t="n">
         <v>-3.79</v>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1495,12 +1607,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1532,17 +1649,22 @@
       <c r="G14" s="4" t="n">
         <v>-5.17</v>
       </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1579,12 +1701,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1621,12 +1748,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1658,17 +1790,22 @@
       <c r="G17" s="4" t="n">
         <v>-1.09</v>
       </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1705,12 +1842,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1747,12 +1889,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1784,17 +1931,22 @@
       <c r="G20" s="4" t="n">
         <v>-1.39</v>
       </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1831,12 +1983,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1873,12 +2030,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1915,12 +2077,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1952,17 +2119,22 @@
       <c r="G24" s="4" t="n">
         <v>-2.96</v>
       </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1999,12 +2171,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2041,12 +2218,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2083,12 +2265,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2125,12 +2312,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2162,17 +2354,22 @@
       <c r="G29" s="4" t="n">
         <v>-5.11</v>
       </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2209,12 +2406,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2246,17 +2448,22 @@
       <c r="G31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2288,17 +2495,22 @@
       <c r="G32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2330,17 +2542,22 @@
       <c r="G33" s="4" t="n">
         <v>-0.38</v>
       </c>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2377,12 +2594,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2414,17 +2636,22 @@
       <c r="G35" s="4" t="n">
         <v>-1.56</v>
       </c>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2461,12 +2688,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2503,12 +2735,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2545,12 +2782,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2587,12 +2829,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2629,12 +2876,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2666,17 +2918,22 @@
       <c r="G41" s="4" t="n">
         <v>-1.23</v>
       </c>
-      <c r="H41" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2708,17 +2965,22 @@
       <c r="G42" s="4" t="n">
         <v>-10</v>
       </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2750,17 +3012,22 @@
       <c r="G43" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2792,17 +3059,22 @@
       <c r="G44" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2839,12 +3111,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2881,12 +3158,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2923,12 +3205,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2965,12 +3252,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3002,17 +3294,22 @@
       <c r="G49" s="4" t="n">
         <v>-0.54</v>
       </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3049,12 +3346,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3091,12 +3393,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3133,12 +3440,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3170,17 +3482,22 @@
       <c r="G53" s="4" t="n">
         <v>-0.89</v>
       </c>
-      <c r="H53" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3217,12 +3534,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3259,12 +3581,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3301,12 +3628,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3343,12 +3675,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3380,17 +3717,22 @@
       <c r="G58" s="4" t="n">
         <v>-7.94</v>
       </c>
-      <c r="H58" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3427,12 +3769,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3464,17 +3811,22 @@
       <c r="G60" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3506,17 +3858,22 @@
       <c r="G61" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3548,17 +3905,22 @@
       <c r="G62" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3595,12 +3957,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3637,12 +4004,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3679,12 +4051,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3716,17 +4093,22 @@
       <c r="G66" s="4" t="n">
         <v>-1.54</v>
       </c>
-      <c r="H66" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3763,12 +4145,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3800,17 +4187,22 @@
       <c r="G68" s="4" t="n">
         <v>-3.54</v>
       </c>
-      <c r="H68" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3847,12 +4239,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3889,12 +4286,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3926,17 +4328,22 @@
       <c r="G71" s="4" t="n">
         <v>-2.65</v>
       </c>
-      <c r="H71" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3973,12 +4380,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4010,17 +4422,22 @@
       <c r="G73" s="4" t="n">
         <v>-1.21</v>
       </c>
-      <c r="H73" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4057,12 +4474,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4099,12 +4521,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4136,17 +4563,22 @@
       <c r="G76" s="4" t="n">
         <v>-2.13</v>
       </c>
-      <c r="H76" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4178,17 +4610,22 @@
       <c r="G77" s="4" t="n">
         <v>-3.39</v>
       </c>
-      <c r="H77" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4225,12 +4662,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4267,12 +4709,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4304,17 +4751,22 @@
       <c r="G80" s="4" t="n">
         <v>-3.49</v>
       </c>
-      <c r="H80" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4351,12 +4803,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4393,12 +4850,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4430,17 +4892,22 @@
       <c r="G83" s="4" t="n">
         <v>-3.36</v>
       </c>
-      <c r="H83" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4477,12 +4944,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4514,17 +4986,22 @@
       <c r="G85" s="4" t="n">
         <v>-2.14</v>
       </c>
-      <c r="H85" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4556,17 +5033,22 @@
       <c r="G86" s="4" t="n">
         <v>-2.99</v>
       </c>
-      <c r="H86" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4598,17 +5080,22 @@
       <c r="G87" s="4" t="n">
         <v>-1.44</v>
       </c>
-      <c r="H87" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4640,17 +5127,22 @@
       <c r="G88" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H88" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4682,17 +5174,22 @@
       <c r="G89" s="4" t="n">
         <v>-5.13</v>
       </c>
-      <c r="H89" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4724,17 +5221,22 @@
       <c r="G90" s="4" t="n">
         <v>-3.7</v>
       </c>
-      <c r="H90" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4771,12 +5273,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4813,12 +5320,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4850,17 +5362,22 @@
       <c r="G93" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H93" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4892,17 +5409,22 @@
       <c r="G94" s="4" t="n">
         <v>-4.95</v>
       </c>
-      <c r="H94" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H94" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4939,12 +5461,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4981,12 +5508,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5023,12 +5555,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5060,17 +5597,22 @@
       <c r="G98" s="4" t="n">
         <v>-1.11</v>
       </c>
-      <c r="H98" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H98" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5102,17 +5644,22 @@
       <c r="G99" s="4" t="n">
         <v>-2.35</v>
       </c>
-      <c r="H99" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5149,12 +5696,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I100" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5186,17 +5738,22 @@
       <c r="G101" s="4" t="n">
         <v>-2.31</v>
       </c>
-      <c r="H101" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5228,17 +5785,22 @@
       <c r="G102" s="4" t="n">
         <v>-0.87</v>
       </c>
-      <c r="H102" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5275,12 +5837,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5317,12 +5884,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I104" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5354,17 +5926,22 @@
       <c r="G105" s="4" t="n">
         <v>-1.69</v>
       </c>
-      <c r="H105" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5401,12 +5978,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5438,17 +6020,22 @@
       <c r="G107" s="4" t="n">
         <v>-0.76</v>
       </c>
-      <c r="H107" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5480,17 +6067,22 @@
       <c r="G108" s="4" t="n">
         <v>-3.41</v>
       </c>
-      <c r="H108" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5527,12 +6119,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5564,17 +6161,22 @@
       <c r="G110" s="4" t="n">
         <v>-1.54</v>
       </c>
-      <c r="H110" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H110" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5606,17 +6208,22 @@
       <c r="G111" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H111" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5653,12 +6260,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5695,12 +6307,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5732,17 +6349,22 @@
       <c r="G114" s="4" t="n">
         <v>-2.78</v>
       </c>
-      <c r="H114" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H114" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5774,17 +6396,22 @@
       <c r="G115" s="4" t="n">
         <v>-4.1</v>
       </c>
-      <c r="H115" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5816,17 +6443,22 @@
       <c r="G116" s="4" t="n">
         <v>-1.1</v>
       </c>
-      <c r="H116" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="H116" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>

--- a/data/performance/daily/signal_list_2026-06-22.xlsx
+++ b/data/performance/daily/signal_list_2026-06-22.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -459,12 +459,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,45 +495,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -553,33 +559,36 @@
         <v>1710</v>
       </c>
       <c r="D5" t="n">
+        <v/>
+      </c>
+      <c r="E5" t="n">
         <v>1720</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>1725</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>0.88</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>0.58</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -600,33 +609,36 @@
         <v>16625</v>
       </c>
       <c r="D6" t="n">
+        <v/>
+      </c>
+      <c r="E6" t="n">
         <v>17000</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>17175</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>3.31</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>2.26</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,33 +659,36 @@
         <v>1510</v>
       </c>
       <c r="D7" t="n">
+        <v/>
+      </c>
+      <c r="E7" t="n">
         <v>1515</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>1520</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>0.66</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>0.33</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -694,33 +709,36 @@
         <v>5879</v>
       </c>
       <c r="D8" t="n">
-        <v>6050</v>
+        <v/>
       </c>
       <c r="E8" t="n">
         <v>6050</v>
       </c>
-      <c r="F8" s="4" t="n">
-        <v>2.91</v>
+      <c r="F8" t="n">
+        <v>6050</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>2.91</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H8" s="4" t="n">
+        <v>2.91</v>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -741,33 +759,36 @@
         <v>955</v>
       </c>
       <c r="D9" t="n">
+        <v/>
+      </c>
+      <c r="E9" t="n">
         <v>955</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>960</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>0.52</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -788,33 +809,36 @@
         <v>1830</v>
       </c>
       <c r="D10" t="n">
+        <v/>
+      </c>
+      <c r="E10" t="n">
         <v>1840</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>1890</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>3.28</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>0.55</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -835,33 +859,36 @@
         <v>705</v>
       </c>
       <c r="D11" t="n">
+        <v/>
+      </c>
+      <c r="E11" t="n">
         <v>700</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>705</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>-0.71</v>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -882,33 +909,36 @@
         <v>7800</v>
       </c>
       <c r="D12" t="n">
+        <v/>
+      </c>
+      <c r="E12" t="n">
         <v>7900</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>9350</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>19.87</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>1.28</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -929,33 +959,36 @@
         <v>460</v>
       </c>
       <c r="D13" t="n">
+        <v/>
+      </c>
+      <c r="E13" t="n">
         <v>474</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>478</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>3.91</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>3.04</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -976,33 +1009,36 @@
         <v>101</v>
       </c>
       <c r="D14" t="n">
+        <v/>
+      </c>
+      <c r="E14" t="n">
         <v>96</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>105</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>3.96</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>-4.95</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1023,33 +1059,36 @@
         <v>710</v>
       </c>
       <c r="D15" t="n">
+        <v/>
+      </c>
+      <c r="E15" t="n">
         <v>660</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>710</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>-7.04</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1070,33 +1109,36 @@
         <v>575</v>
       </c>
       <c r="D16" t="n">
+        <v/>
+      </c>
+      <c r="E16" t="n">
         <v>570</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>580</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>0.87</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>-0.87</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1113,7 +1155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K116"/>
+  <dimension ref="A1:L116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1121,12 +1163,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1156,45 +1199,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1215,33 +1263,36 @@
         <v>910</v>
       </c>
       <c r="D5" t="n">
+        <v/>
+      </c>
+      <c r="E5" t="n">
         <v>865</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>950</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>4.4</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>-4.95</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1262,33 +1313,36 @@
         <v>408.3</v>
       </c>
       <c r="D6" t="n">
+        <v/>
+      </c>
+      <c r="E6" t="n">
         <v>398</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>454</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>11.19</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>-2.52</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1309,33 +1363,36 @@
         <v>165</v>
       </c>
       <c r="D7" t="n">
+        <v/>
+      </c>
+      <c r="E7" t="n">
         <v>162</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>170</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>3.03</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>-1.82</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1356,33 +1413,36 @@
         <v>6300</v>
       </c>
       <c r="D8" t="n">
+        <v/>
+      </c>
+      <c r="E8" t="n">
         <v>6200</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>6400</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>1.59</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>-1.59</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1403,33 +1463,36 @@
         <v>145</v>
       </c>
       <c r="D9" t="n">
+        <v/>
+      </c>
+      <c r="E9" t="n">
         <v>139</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>173</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>19.31</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>-4.14</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1450,33 +1513,36 @@
         <v>1675</v>
       </c>
       <c r="D10" t="n">
+        <v/>
+      </c>
+      <c r="E10" t="n">
         <v>1670</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>1695</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>1.19</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>-0.3</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1497,33 +1563,36 @@
         <v>314</v>
       </c>
       <c r="D11" t="n">
+        <v/>
+      </c>
+      <c r="E11" t="n">
         <v>298</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>346</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>10.19</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>-5.1</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1544,33 +1613,36 @@
         <v>660</v>
       </c>
       <c r="D12" t="n">
+        <v/>
+      </c>
+      <c r="E12" t="n">
         <v>635</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>670</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>1.52</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>-3.79</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1591,33 +1663,36 @@
         <v>1280</v>
       </c>
       <c r="D13" t="n">
+        <v/>
+      </c>
+      <c r="E13" t="n">
         <v>1210</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>1280</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>-5.47</v>
       </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1638,33 +1713,36 @@
         <v>870</v>
       </c>
       <c r="D14" t="n">
+        <v/>
+      </c>
+      <c r="E14" t="n">
         <v>825</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>880</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>1.15</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>-5.17</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1685,33 +1763,36 @@
         <v>11000</v>
       </c>
       <c r="D15" t="n">
+        <v/>
+      </c>
+      <c r="E15" t="n">
         <v>11675</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>12000</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>9.09</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>6.14</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1732,33 +1813,36 @@
         <v>2380</v>
       </c>
       <c r="D16" t="n">
-        <v>2400</v>
+        <v/>
       </c>
       <c r="E16" t="n">
         <v>2400</v>
       </c>
-      <c r="F16" s="4" t="n">
-        <v>0.84</v>
+      <c r="F16" t="n">
+        <v>2400</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>0.84</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H16" s="4" t="n">
+        <v>0.84</v>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1779,33 +1863,36 @@
         <v>366</v>
       </c>
       <c r="D17" t="n">
+        <v/>
+      </c>
+      <c r="E17" t="n">
         <v>362</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>370</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>1.09</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>-1.09</v>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1826,33 +1913,36 @@
         <v>1710</v>
       </c>
       <c r="D18" t="n">
+        <v/>
+      </c>
+      <c r="E18" t="n">
         <v>1720</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>1725</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>0.88</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>0.58</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1873,33 +1963,36 @@
         <v>290</v>
       </c>
       <c r="D19" t="n">
+        <v/>
+      </c>
+      <c r="E19" t="n">
         <v>284</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>290</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>-2.07</v>
       </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1920,33 +2013,36 @@
         <v>72</v>
       </c>
       <c r="D20" t="n">
+        <v/>
+      </c>
+      <c r="E20" t="n">
         <v>71</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>74</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>2.78</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <v>-1.39</v>
       </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1967,33 +2063,36 @@
         <v>850</v>
       </c>
       <c r="D21" t="n">
+        <v/>
+      </c>
+      <c r="E21" t="n">
         <v>870</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>885</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="G21" s="4" t="n">
         <v>4.12</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="H21" s="4" t="n">
         <v>2.35</v>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2014,33 +2113,36 @@
         <v>16625</v>
       </c>
       <c r="D22" t="n">
+        <v/>
+      </c>
+      <c r="E22" t="n">
         <v>17000</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>17175</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="G22" s="4" t="n">
         <v>3.31</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="H22" s="4" t="n">
         <v>2.26</v>
       </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2061,33 +2163,36 @@
         <v>1200</v>
       </c>
       <c r="D23" t="n">
+        <v/>
+      </c>
+      <c r="E23" t="n">
         <v>1175</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>1195</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>-0.42</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="H23" s="4" t="n">
         <v>-2.08</v>
       </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2108,33 +2213,36 @@
         <v>270</v>
       </c>
       <c r="D24" t="n">
+        <v/>
+      </c>
+      <c r="E24" t="n">
         <v>262</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>280</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="G24" s="4" t="n">
         <v>3.7</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="H24" s="4" t="n">
         <v>-2.96</v>
       </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2155,33 +2263,36 @@
         <v>825</v>
       </c>
       <c r="D25" t="n">
+        <v/>
+      </c>
+      <c r="E25" t="n">
         <v>860</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>870</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="G25" s="4" t="n">
         <v>5.45</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>4.24</v>
       </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2202,33 +2313,36 @@
         <v>75</v>
       </c>
       <c r="D26" t="n">
+        <v/>
+      </c>
+      <c r="E26" t="n">
         <v>80</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>82</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="G26" s="4" t="n">
         <v>9.33</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <v>6.67</v>
       </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2249,33 +2363,36 @@
         <v>6725</v>
       </c>
       <c r="D27" t="n">
+        <v/>
+      </c>
+      <c r="E27" t="n">
         <v>6800</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>6825</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="G27" s="4" t="n">
         <v>1.49</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="H27" s="4" t="n">
         <v>1.12</v>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2296,33 +2413,36 @@
         <v>700</v>
       </c>
       <c r="D28" t="n">
+        <v/>
+      </c>
+      <c r="E28" t="n">
         <v>670</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>680</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="G28" s="4" t="n">
         <v>-2.86</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="H28" s="4" t="n">
         <v>-4.29</v>
       </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2343,33 +2463,36 @@
         <v>470</v>
       </c>
       <c r="D29" t="n">
+        <v/>
+      </c>
+      <c r="E29" t="n">
         <v>446</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>478</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="G29" s="4" t="n">
         <v>1.7</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="H29" s="4" t="n">
         <v>-5.11</v>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2390,33 +2513,36 @@
         <v>1340</v>
       </c>
       <c r="D30" t="n">
+        <v/>
+      </c>
+      <c r="E30" t="n">
         <v>1355</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>1450</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="G30" s="4" t="n">
         <v>8.210000000000001</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="H30" s="4" t="n">
         <v>1.12</v>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2437,33 +2563,36 @@
         <v>286</v>
       </c>
       <c r="D31" t="n">
+        <v/>
+      </c>
+      <c r="E31" t="n">
         <v>286</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>288</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="G31" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="H31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2484,33 +2613,36 @@
         <v>795</v>
       </c>
       <c r="D32" t="n">
+        <v/>
+      </c>
+      <c r="E32" t="n">
         <v>795</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>800</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="G32" s="4" t="n">
         <v>0.63</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="H32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2531,33 +2663,36 @@
         <v>2620</v>
       </c>
       <c r="D33" t="n">
+        <v/>
+      </c>
+      <c r="E33" t="n">
         <v>2610</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>2650</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="G33" s="4" t="n">
         <v>1.15</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="H33" s="4" t="n">
         <v>-0.38</v>
       </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2578,33 +2713,36 @@
         <v>2930</v>
       </c>
       <c r="D34" t="n">
+        <v/>
+      </c>
+      <c r="E34" t="n">
         <v>2980</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>3020</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="G34" s="4" t="n">
         <v>3.07</v>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="H34" s="4" t="n">
         <v>1.71</v>
       </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2625,33 +2763,36 @@
         <v>1600</v>
       </c>
       <c r="D35" t="n">
+        <v/>
+      </c>
+      <c r="E35" t="n">
         <v>1575</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>1615</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="G35" s="4" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="H35" s="4" t="n">
         <v>-1.56</v>
       </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2672,33 +2813,36 @@
         <v>21825</v>
       </c>
       <c r="D36" t="n">
-        <v>22025</v>
+        <v/>
       </c>
       <c r="E36" t="n">
         <v>22025</v>
       </c>
-      <c r="F36" s="4" t="n">
-        <v>0.92</v>
+      <c r="F36" t="n">
+        <v>22025</v>
       </c>
       <c r="G36" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H36" s="4" t="n">
+        <v>0.92</v>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2719,33 +2863,36 @@
         <v>52</v>
       </c>
       <c r="D37" t="n">
-        <v>52</v>
+        <v/>
       </c>
       <c r="E37" t="n">
         <v>52</v>
       </c>
-      <c r="F37" s="4" t="n">
-        <v>0</v>
+      <c r="F37" t="n">
+        <v>52</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H37" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2766,33 +2913,36 @@
         <v>1990</v>
       </c>
       <c r="D38" t="n">
+        <v/>
+      </c>
+      <c r="E38" t="n">
         <v>1865</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>1950</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="G38" s="4" t="n">
         <v>-2.01</v>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="H38" s="4" t="n">
         <v>-6.28</v>
       </c>
-      <c r="H38" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2813,33 +2963,36 @@
         <v>1830</v>
       </c>
       <c r="D39" t="n">
+        <v/>
+      </c>
+      <c r="E39" t="n">
         <v>1840</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>1890</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="G39" s="4" t="n">
         <v>3.28</v>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="H39" s="4" t="n">
         <v>0.55</v>
       </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2860,33 +3013,36 @@
         <v>94</v>
       </c>
       <c r="D40" t="n">
+        <v/>
+      </c>
+      <c r="E40" t="n">
         <v>99</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>112</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="G40" s="4" t="n">
         <v>19.15</v>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="H40" s="4" t="n">
         <v>5.32</v>
       </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2907,33 +3063,36 @@
         <v>162</v>
       </c>
       <c r="D41" t="n">
+        <v/>
+      </c>
+      <c r="E41" t="n">
         <v>160</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>163</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="G41" s="4" t="n">
         <v>0.62</v>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="H41" s="4" t="n">
         <v>-1.23</v>
       </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2954,33 +3113,36 @@
         <v>2150</v>
       </c>
       <c r="D42" t="n">
+        <v/>
+      </c>
+      <c r="E42" t="n">
         <v>1935</v>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>2160</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="G42" s="4" t="n">
         <v>0.47</v>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="H42" s="4" t="n">
         <v>-10</v>
       </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3001,33 +3163,36 @@
         <v>71</v>
       </c>
       <c r="D43" t="n">
+        <v/>
+      </c>
+      <c r="E43" t="n">
         <v>71</v>
       </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
         <v>75</v>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="G43" s="4" t="n">
         <v>5.63</v>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="H43" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3048,33 +3213,36 @@
         <v>1515</v>
       </c>
       <c r="D44" t="n">
+        <v/>
+      </c>
+      <c r="E44" t="n">
         <v>1515</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>1530</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="G44" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="H44" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3095,33 +3263,36 @@
         <v>665</v>
       </c>
       <c r="D45" t="n">
-        <v>665</v>
+        <v/>
       </c>
       <c r="E45" t="n">
         <v>665</v>
       </c>
-      <c r="F45" s="4" t="n">
-        <v>0</v>
+      <c r="F45" t="n">
+        <v>665</v>
       </c>
       <c r="G45" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H45" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3142,33 +3313,36 @@
         <v>3490</v>
       </c>
       <c r="D46" t="n">
+        <v/>
+      </c>
+      <c r="E46" t="n">
         <v>3730</v>
       </c>
-      <c r="E46" t="n">
+      <c r="F46" t="n">
         <v>3750</v>
       </c>
-      <c r="F46" s="4" t="n">
+      <c r="G46" s="4" t="n">
         <v>7.45</v>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="H46" s="4" t="n">
         <v>6.88</v>
       </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3189,33 +3363,36 @@
         <v>595</v>
       </c>
       <c r="D47" t="n">
+        <v/>
+      </c>
+      <c r="E47" t="n">
         <v>555</v>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>560</v>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="G47" s="4" t="n">
         <v>-5.88</v>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="H47" s="4" t="n">
         <v>-6.72</v>
       </c>
-      <c r="H47" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3236,33 +3413,36 @@
         <v>5975</v>
       </c>
       <c r="D48" t="n">
+        <v/>
+      </c>
+      <c r="E48" t="n">
         <v>6000</v>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>6100</v>
       </c>
-      <c r="F48" s="4" t="n">
+      <c r="G48" s="4" t="n">
         <v>2.09</v>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="H48" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3283,33 +3463,36 @@
         <v>372</v>
       </c>
       <c r="D49" t="n">
+        <v/>
+      </c>
+      <c r="E49" t="n">
         <v>370</v>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
         <v>376</v>
       </c>
-      <c r="F49" s="4" t="n">
+      <c r="G49" s="4" t="n">
         <v>1.08</v>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="H49" s="4" t="n">
         <v>-0.54</v>
       </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3330,33 +3513,36 @@
         <v>555</v>
       </c>
       <c r="D50" t="n">
+        <v/>
+      </c>
+      <c r="E50" t="n">
         <v>560</v>
       </c>
-      <c r="E50" t="n">
+      <c r="F50" t="n">
         <v>570</v>
       </c>
-      <c r="F50" s="4" t="n">
+      <c r="G50" s="4" t="n">
         <v>2.7</v>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="H50" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3377,33 +3563,36 @@
         <v>168</v>
       </c>
       <c r="D51" t="n">
+        <v/>
+      </c>
+      <c r="E51" t="n">
         <v>170</v>
       </c>
-      <c r="E51" t="n">
+      <c r="F51" t="n">
         <v>171</v>
       </c>
-      <c r="F51" s="4" t="n">
+      <c r="G51" s="4" t="n">
         <v>1.79</v>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="H51" s="4" t="n">
         <v>1.19</v>
       </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3424,33 +3613,36 @@
         <v>1685</v>
       </c>
       <c r="D52" t="n">
+        <v/>
+      </c>
+      <c r="E52" t="n">
         <v>1690</v>
       </c>
-      <c r="E52" t="n">
+      <c r="F52" t="n">
         <v>1725</v>
       </c>
-      <c r="F52" s="4" t="n">
+      <c r="G52" s="4" t="n">
         <v>2.37</v>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="H52" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3471,33 +3663,36 @@
         <v>1680</v>
       </c>
       <c r="D53" t="n">
+        <v/>
+      </c>
+      <c r="E53" t="n">
         <v>1665</v>
       </c>
-      <c r="E53" t="n">
+      <c r="F53" t="n">
         <v>1685</v>
       </c>
-      <c r="F53" s="4" t="n">
+      <c r="G53" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="H53" s="4" t="n">
         <v>-0.89</v>
       </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3518,33 +3713,36 @@
         <v>1345</v>
       </c>
       <c r="D54" t="n">
-        <v>1400</v>
+        <v/>
       </c>
       <c r="E54" t="n">
         <v>1400</v>
       </c>
-      <c r="F54" s="4" t="n">
-        <v>4.09</v>
+      <c r="F54" t="n">
+        <v>1400</v>
       </c>
       <c r="G54" s="4" t="n">
         <v>4.09</v>
       </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H54" s="4" t="n">
+        <v>4.09</v>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3565,33 +3763,36 @@
         <v>7800</v>
       </c>
       <c r="D55" t="n">
+        <v/>
+      </c>
+      <c r="E55" t="n">
         <v>7900</v>
       </c>
-      <c r="E55" t="n">
+      <c r="F55" t="n">
         <v>9350</v>
       </c>
-      <c r="F55" s="4" t="n">
+      <c r="G55" s="4" t="n">
         <v>19.87</v>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="H55" s="4" t="n">
         <v>1.28</v>
       </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3612,33 +3813,36 @@
         <v>189</v>
       </c>
       <c r="D56" t="n">
-        <v>187</v>
+        <v/>
       </c>
       <c r="E56" t="n">
         <v>187</v>
       </c>
-      <c r="F56" s="4" t="n">
-        <v>-1.06</v>
+      <c r="F56" t="n">
+        <v>187</v>
       </c>
       <c r="G56" s="4" t="n">
         <v>-1.06</v>
       </c>
-      <c r="H56" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H56" s="4" t="n">
+        <v>-1.06</v>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3659,33 +3863,36 @@
         <v>430</v>
       </c>
       <c r="D57" t="n">
+        <v/>
+      </c>
+      <c r="E57" t="n">
         <v>432</v>
       </c>
-      <c r="E57" t="n">
+      <c r="F57" t="n">
         <v>460</v>
       </c>
-      <c r="F57" s="4" t="n">
+      <c r="G57" s="4" t="n">
         <v>6.98</v>
       </c>
-      <c r="G57" s="4" t="n">
+      <c r="H57" s="4" t="n">
         <v>0.47</v>
       </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3706,33 +3913,36 @@
         <v>630</v>
       </c>
       <c r="D58" t="n">
+        <v/>
+      </c>
+      <c r="E58" t="n">
         <v>580</v>
       </c>
-      <c r="E58" t="n">
+      <c r="F58" t="n">
         <v>645</v>
       </c>
-      <c r="F58" s="4" t="n">
+      <c r="G58" s="4" t="n">
         <v>2.38</v>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="H58" s="4" t="n">
         <v>-7.94</v>
       </c>
-      <c r="H58" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I58" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3753,33 +3963,36 @@
         <v>1163.31</v>
       </c>
       <c r="D59" t="n">
+        <v/>
+      </c>
+      <c r="E59" t="n">
         <v>1185</v>
       </c>
-      <c r="E59" t="n">
+      <c r="F59" t="n">
         <v>1195</v>
       </c>
-      <c r="F59" s="4" t="n">
+      <c r="G59" s="4" t="n">
         <v>2.72</v>
       </c>
-      <c r="G59" s="4" t="n">
+      <c r="H59" s="4" t="n">
         <v>1.86</v>
       </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3800,33 +4013,36 @@
         <v>172</v>
       </c>
       <c r="D60" t="n">
+        <v/>
+      </c>
+      <c r="E60" t="n">
         <v>172</v>
       </c>
-      <c r="E60" t="n">
+      <c r="F60" t="n">
         <v>183</v>
       </c>
-      <c r="F60" s="4" t="n">
+      <c r="G60" s="4" t="n">
         <v>6.4</v>
       </c>
-      <c r="G60" s="4" t="n">
+      <c r="H60" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I60" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3847,33 +4063,36 @@
         <v>85</v>
       </c>
       <c r="D61" t="n">
+        <v/>
+      </c>
+      <c r="E61" t="n">
         <v>85</v>
       </c>
-      <c r="E61" t="n">
+      <c r="F61" t="n">
         <v>88</v>
       </c>
-      <c r="F61" s="4" t="n">
+      <c r="G61" s="4" t="n">
         <v>3.53</v>
       </c>
-      <c r="G61" s="4" t="n">
+      <c r="H61" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I61" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3894,33 +4113,36 @@
         <v>160</v>
       </c>
       <c r="D62" t="n">
+        <v/>
+      </c>
+      <c r="E62" t="n">
         <v>160</v>
       </c>
-      <c r="E62" t="n">
+      <c r="F62" t="n">
         <v>169</v>
       </c>
-      <c r="F62" s="4" t="n">
+      <c r="G62" s="4" t="n">
         <v>5.62</v>
       </c>
-      <c r="G62" s="4" t="n">
+      <c r="H62" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I62" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3941,33 +4163,36 @@
         <v>254</v>
       </c>
       <c r="D63" t="n">
+        <v/>
+      </c>
+      <c r="E63" t="n">
         <v>256</v>
       </c>
-      <c r="E63" t="n">
+      <c r="F63" t="n">
         <v>268</v>
       </c>
-      <c r="F63" s="4" t="n">
+      <c r="G63" s="4" t="n">
         <v>5.51</v>
       </c>
-      <c r="G63" s="4" t="n">
+      <c r="H63" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="H63" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3988,33 +4213,36 @@
         <v>13800</v>
       </c>
       <c r="D64" t="n">
+        <v/>
+      </c>
+      <c r="E64" t="n">
         <v>13975</v>
       </c>
-      <c r="E64" t="n">
+      <c r="F64" t="n">
         <v>16000</v>
       </c>
-      <c r="F64" s="4" t="n">
+      <c r="G64" s="4" t="n">
         <v>15.94</v>
       </c>
-      <c r="G64" s="4" t="n">
+      <c r="H64" s="4" t="n">
         <v>1.27</v>
       </c>
-      <c r="H64" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4035,33 +4263,36 @@
         <v>100</v>
       </c>
       <c r="D65" t="n">
+        <v/>
+      </c>
+      <c r="E65" t="n">
         <v>104</v>
       </c>
-      <c r="E65" t="n">
+      <c r="F65" t="n">
         <v>115</v>
       </c>
-      <c r="F65" s="4" t="n">
+      <c r="G65" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="G65" s="4" t="n">
+      <c r="H65" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H65" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4082,33 +4313,36 @@
         <v>65</v>
       </c>
       <c r="D66" t="n">
+        <v/>
+      </c>
+      <c r="E66" t="n">
         <v>64</v>
       </c>
-      <c r="E66" t="n">
+      <c r="F66" t="n">
         <v>66</v>
       </c>
-      <c r="F66" s="4" t="n">
+      <c r="G66" s="4" t="n">
         <v>1.54</v>
       </c>
-      <c r="G66" s="4" t="n">
+      <c r="H66" s="4" t="n">
         <v>-1.54</v>
       </c>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I66" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4129,33 +4363,36 @@
         <v>134</v>
       </c>
       <c r="D67" t="n">
+        <v/>
+      </c>
+      <c r="E67" t="n">
         <v>150</v>
       </c>
-      <c r="E67" t="n">
+      <c r="F67" t="n">
         <v>156</v>
       </c>
-      <c r="F67" s="4" t="n">
+      <c r="G67" s="4" t="n">
         <v>16.42</v>
       </c>
-      <c r="G67" s="4" t="n">
+      <c r="H67" s="4" t="n">
         <v>11.94</v>
       </c>
-      <c r="H67" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4176,33 +4413,36 @@
         <v>1555</v>
       </c>
       <c r="D68" t="n">
+        <v/>
+      </c>
+      <c r="E68" t="n">
         <v>1500</v>
       </c>
-      <c r="E68" t="n">
+      <c r="F68" t="n">
         <v>1600</v>
       </c>
-      <c r="F68" s="4" t="n">
+      <c r="G68" s="4" t="n">
         <v>2.89</v>
       </c>
-      <c r="G68" s="4" t="n">
+      <c r="H68" s="4" t="n">
         <v>-3.54</v>
       </c>
-      <c r="H68" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I68" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4223,33 +4463,36 @@
         <v>1300</v>
       </c>
       <c r="D69" t="n">
-        <v>1335</v>
+        <v/>
       </c>
       <c r="E69" t="n">
         <v>1335</v>
       </c>
-      <c r="F69" s="4" t="n">
-        <v>2.69</v>
+      <c r="F69" t="n">
+        <v>1335</v>
       </c>
       <c r="G69" s="4" t="n">
         <v>2.69</v>
       </c>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H69" s="4" t="n">
+        <v>2.69</v>
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4270,33 +4513,36 @@
         <v>68</v>
       </c>
       <c r="D70" t="n">
+        <v/>
+      </c>
+      <c r="E70" t="n">
         <v>70</v>
       </c>
-      <c r="E70" t="n">
+      <c r="F70" t="n">
         <v>74</v>
       </c>
-      <c r="F70" s="4" t="n">
+      <c r="G70" s="4" t="n">
         <v>8.82</v>
       </c>
-      <c r="G70" s="4" t="n">
+      <c r="H70" s="4" t="n">
         <v>2.94</v>
       </c>
-      <c r="H70" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4317,33 +4563,36 @@
         <v>151</v>
       </c>
       <c r="D71" t="n">
+        <v/>
+      </c>
+      <c r="E71" t="n">
         <v>147</v>
       </c>
-      <c r="E71" t="n">
+      <c r="F71" t="n">
         <v>153</v>
       </c>
-      <c r="F71" s="4" t="n">
+      <c r="G71" s="4" t="n">
         <v>1.32</v>
       </c>
-      <c r="G71" s="4" t="n">
+      <c r="H71" s="4" t="n">
         <v>-2.65</v>
       </c>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4364,33 +4613,36 @@
         <v>1775</v>
       </c>
       <c r="D72" t="n">
+        <v/>
+      </c>
+      <c r="E72" t="n">
         <v>1850</v>
       </c>
-      <c r="E72" t="n">
+      <c r="F72" t="n">
         <v>2140</v>
       </c>
-      <c r="F72" s="4" t="n">
+      <c r="G72" s="4" t="n">
         <v>20.56</v>
       </c>
-      <c r="G72" s="4" t="n">
+      <c r="H72" s="4" t="n">
         <v>4.23</v>
       </c>
-      <c r="H72" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4411,33 +4663,36 @@
         <v>494</v>
       </c>
       <c r="D73" t="n">
+        <v/>
+      </c>
+      <c r="E73" t="n">
         <v>488</v>
       </c>
-      <c r="E73" t="n">
+      <c r="F73" t="n">
         <v>500</v>
       </c>
-      <c r="F73" s="4" t="n">
+      <c r="G73" s="4" t="n">
         <v>1.21</v>
       </c>
-      <c r="G73" s="4" t="n">
+      <c r="H73" s="4" t="n">
         <v>-1.21</v>
       </c>
-      <c r="H73" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4458,33 +4713,36 @@
         <v>133</v>
       </c>
       <c r="D74" t="n">
+        <v/>
+      </c>
+      <c r="E74" t="n">
         <v>134</v>
       </c>
-      <c r="E74" t="n">
+      <c r="F74" t="n">
         <v>135</v>
       </c>
-      <c r="F74" s="4" t="n">
+      <c r="G74" s="4" t="n">
         <v>1.5</v>
       </c>
-      <c r="G74" s="4" t="n">
+      <c r="H74" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="H74" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4505,33 +4763,36 @@
         <v>1505</v>
       </c>
       <c r="D75" t="n">
+        <v/>
+      </c>
+      <c r="E75" t="n">
         <v>1355</v>
       </c>
-      <c r="E75" t="n">
+      <c r="F75" t="n">
         <v>1505</v>
       </c>
-      <c r="F75" s="4" t="n">
+      <c r="G75" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G75" s="4" t="n">
+      <c r="H75" s="4" t="n">
         <v>-9.970000000000001</v>
       </c>
-      <c r="H75" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4552,33 +4813,36 @@
         <v>94</v>
       </c>
       <c r="D76" t="n">
+        <v/>
+      </c>
+      <c r="E76" t="n">
         <v>92</v>
       </c>
-      <c r="E76" t="n">
+      <c r="F76" t="n">
         <v>95</v>
       </c>
-      <c r="F76" s="4" t="n">
+      <c r="G76" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="G76" s="4" t="n">
+      <c r="H76" s="4" t="n">
         <v>-2.13</v>
       </c>
-      <c r="H76" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I76" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4599,33 +4863,36 @@
         <v>590</v>
       </c>
       <c r="D77" t="n">
+        <v/>
+      </c>
+      <c r="E77" t="n">
         <v>570</v>
       </c>
-      <c r="E77" t="n">
+      <c r="F77" t="n">
         <v>595</v>
       </c>
-      <c r="F77" s="4" t="n">
+      <c r="G77" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="G77" s="4" t="n">
+      <c r="H77" s="4" t="n">
         <v>-3.39</v>
       </c>
-      <c r="H77" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I77" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4646,33 +4913,36 @@
         <v>192</v>
       </c>
       <c r="D78" t="n">
+        <v/>
+      </c>
+      <c r="E78" t="n">
         <v>182</v>
       </c>
-      <c r="E78" t="n">
+      <c r="F78" t="n">
         <v>190</v>
       </c>
-      <c r="F78" s="4" t="n">
+      <c r="G78" s="4" t="n">
         <v>-1.04</v>
       </c>
-      <c r="G78" s="4" t="n">
+      <c r="H78" s="4" t="n">
         <v>-5.21</v>
       </c>
-      <c r="H78" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4693,33 +4963,36 @@
         <v>460</v>
       </c>
       <c r="D79" t="n">
+        <v/>
+      </c>
+      <c r="E79" t="n">
         <v>474</v>
       </c>
-      <c r="E79" t="n">
+      <c r="F79" t="n">
         <v>478</v>
       </c>
-      <c r="F79" s="4" t="n">
+      <c r="G79" s="4" t="n">
         <v>3.91</v>
       </c>
-      <c r="G79" s="4" t="n">
+      <c r="H79" s="4" t="n">
         <v>3.04</v>
       </c>
-      <c r="H79" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4740,33 +5013,36 @@
         <v>6450</v>
       </c>
       <c r="D80" t="n">
+        <v/>
+      </c>
+      <c r="E80" t="n">
         <v>6225</v>
       </c>
-      <c r="E80" t="n">
+      <c r="F80" t="n">
         <v>6600</v>
       </c>
-      <c r="F80" s="4" t="n">
+      <c r="G80" s="4" t="n">
         <v>2.33</v>
       </c>
-      <c r="G80" s="4" t="n">
+      <c r="H80" s="4" t="n">
         <v>-3.49</v>
       </c>
-      <c r="H80" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I80" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4787,33 +5063,36 @@
         <v>346</v>
       </c>
       <c r="D81" t="n">
+        <v/>
+      </c>
+      <c r="E81" t="n">
         <v>352</v>
       </c>
-      <c r="E81" t="n">
+      <c r="F81" t="n">
         <v>354</v>
       </c>
-      <c r="F81" s="4" t="n">
+      <c r="G81" s="4" t="n">
         <v>2.31</v>
       </c>
-      <c r="G81" s="4" t="n">
+      <c r="H81" s="4" t="n">
         <v>1.73</v>
       </c>
-      <c r="H81" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4834,33 +5113,36 @@
         <v>2030</v>
       </c>
       <c r="D82" t="n">
+        <v/>
+      </c>
+      <c r="E82" t="n">
         <v>2070</v>
       </c>
-      <c r="E82" t="n">
+      <c r="F82" t="n">
         <v>2320</v>
       </c>
-      <c r="F82" s="4" t="n">
+      <c r="G82" s="4" t="n">
         <v>14.29</v>
       </c>
-      <c r="G82" s="4" t="n">
+      <c r="H82" s="4" t="n">
         <v>1.97</v>
       </c>
-      <c r="H82" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4881,33 +5163,36 @@
         <v>745</v>
       </c>
       <c r="D83" t="n">
+        <v/>
+      </c>
+      <c r="E83" t="n">
         <v>720</v>
       </c>
-      <c r="E83" t="n">
+      <c r="F83" t="n">
         <v>790</v>
       </c>
-      <c r="F83" s="4" t="n">
+      <c r="G83" s="4" t="n">
         <v>6.04</v>
       </c>
-      <c r="G83" s="4" t="n">
+      <c r="H83" s="4" t="n">
         <v>-3.36</v>
       </c>
-      <c r="H83" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I83" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4928,33 +5213,36 @@
         <v>210</v>
       </c>
       <c r="D84" t="n">
-        <v>212</v>
+        <v/>
       </c>
       <c r="E84" t="n">
         <v>212</v>
       </c>
-      <c r="F84" s="4" t="n">
-        <v>0.95</v>
+      <c r="F84" t="n">
+        <v>212</v>
       </c>
       <c r="G84" s="4" t="n">
         <v>0.95</v>
       </c>
-      <c r="H84" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H84" s="4" t="n">
+        <v>0.95</v>
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4975,33 +5263,36 @@
         <v>187</v>
       </c>
       <c r="D85" t="n">
+        <v/>
+      </c>
+      <c r="E85" t="n">
         <v>183</v>
       </c>
-      <c r="E85" t="n">
+      <c r="F85" t="n">
         <v>189</v>
       </c>
-      <c r="F85" s="4" t="n">
+      <c r="G85" s="4" t="n">
         <v>1.07</v>
       </c>
-      <c r="G85" s="4" t="n">
+      <c r="H85" s="4" t="n">
         <v>-2.14</v>
       </c>
-      <c r="H85" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I85" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5022,33 +5313,36 @@
         <v>67</v>
       </c>
       <c r="D86" t="n">
+        <v/>
+      </c>
+      <c r="E86" t="n">
         <v>65</v>
       </c>
-      <c r="E86" t="n">
+      <c r="F86" t="n">
         <v>68</v>
       </c>
-      <c r="F86" s="4" t="n">
+      <c r="G86" s="4" t="n">
         <v>1.49</v>
       </c>
-      <c r="G86" s="4" t="n">
+      <c r="H86" s="4" t="n">
         <v>-2.99</v>
       </c>
-      <c r="H86" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I86" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5069,33 +5363,36 @@
         <v>139</v>
       </c>
       <c r="D87" t="n">
+        <v/>
+      </c>
+      <c r="E87" t="n">
         <v>137</v>
       </c>
-      <c r="E87" t="n">
+      <c r="F87" t="n">
         <v>142</v>
       </c>
-      <c r="F87" s="4" t="n">
+      <c r="G87" s="4" t="n">
         <v>2.16</v>
       </c>
-      <c r="G87" s="4" t="n">
+      <c r="H87" s="4" t="n">
         <v>-1.44</v>
       </c>
-      <c r="H87" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I87" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5116,33 +5413,36 @@
         <v>98</v>
       </c>
       <c r="D88" t="n">
+        <v/>
+      </c>
+      <c r="E88" t="n">
         <v>98</v>
       </c>
-      <c r="E88" t="n">
+      <c r="F88" t="n">
         <v>106</v>
       </c>
-      <c r="F88" s="4" t="n">
+      <c r="G88" s="4" t="n">
         <v>8.16</v>
       </c>
-      <c r="G88" s="4" t="n">
+      <c r="H88" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H88" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I88" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5163,33 +5463,36 @@
         <v>585</v>
       </c>
       <c r="D89" t="n">
+        <v/>
+      </c>
+      <c r="E89" t="n">
         <v>555</v>
       </c>
-      <c r="E89" t="n">
+      <c r="F89" t="n">
         <v>615</v>
       </c>
-      <c r="F89" s="4" t="n">
+      <c r="G89" s="4" t="n">
         <v>5.13</v>
       </c>
-      <c r="G89" s="4" t="n">
+      <c r="H89" s="4" t="n">
         <v>-5.13</v>
       </c>
-      <c r="H89" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I89" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J89" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5210,33 +5513,36 @@
         <v>270</v>
       </c>
       <c r="D90" t="n">
+        <v/>
+      </c>
+      <c r="E90" t="n">
         <v>260</v>
       </c>
-      <c r="E90" t="n">
+      <c r="F90" t="n">
         <v>282</v>
       </c>
-      <c r="F90" s="4" t="n">
+      <c r="G90" s="4" t="n">
         <v>4.44</v>
       </c>
-      <c r="G90" s="4" t="n">
+      <c r="H90" s="4" t="n">
         <v>-3.7</v>
       </c>
-      <c r="H90" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I90" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5257,33 +5563,36 @@
         <v>650</v>
       </c>
       <c r="D91" t="n">
-        <v>660</v>
+        <v/>
       </c>
       <c r="E91" t="n">
         <v>660</v>
       </c>
-      <c r="F91" s="4" t="n">
-        <v>1.54</v>
+      <c r="F91" t="n">
+        <v>660</v>
       </c>
       <c r="G91" s="4" t="n">
         <v>1.54</v>
       </c>
-      <c r="H91" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H91" s="4" t="n">
+        <v>1.54</v>
       </c>
       <c r="I91" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J91" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5304,33 +5613,36 @@
         <v>116</v>
       </c>
       <c r="D92" t="n">
+        <v/>
+      </c>
+      <c r="E92" t="n">
         <v>117</v>
       </c>
-      <c r="E92" t="n">
+      <c r="F92" t="n">
         <v>120</v>
       </c>
-      <c r="F92" s="4" t="n">
+      <c r="G92" s="4" t="n">
         <v>3.45</v>
       </c>
-      <c r="G92" s="4" t="n">
+      <c r="H92" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="H92" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I92" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5351,33 +5663,36 @@
         <v>59</v>
       </c>
       <c r="D93" t="n">
+        <v/>
+      </c>
+      <c r="E93" t="n">
         <v>59</v>
       </c>
-      <c r="E93" t="n">
+      <c r="F93" t="n">
         <v>60</v>
       </c>
-      <c r="F93" s="4" t="n">
+      <c r="G93" s="4" t="n">
         <v>1.69</v>
       </c>
-      <c r="G93" s="4" t="n">
+      <c r="H93" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H93" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I93" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J93" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5398,33 +5713,36 @@
         <v>101</v>
       </c>
       <c r="D94" t="n">
+        <v/>
+      </c>
+      <c r="E94" t="n">
         <v>96</v>
       </c>
-      <c r="E94" t="n">
+      <c r="F94" t="n">
         <v>105</v>
       </c>
-      <c r="F94" s="4" t="n">
+      <c r="G94" s="4" t="n">
         <v>3.96</v>
       </c>
-      <c r="G94" s="4" t="n">
+      <c r="H94" s="4" t="n">
         <v>-4.95</v>
       </c>
-      <c r="H94" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I94" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J94" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5445,33 +5763,36 @@
         <v>240</v>
       </c>
       <c r="D95" t="n">
+        <v/>
+      </c>
+      <c r="E95" t="n">
         <v>232</v>
       </c>
-      <c r="E95" t="n">
+      <c r="F95" t="n">
         <v>234</v>
       </c>
-      <c r="F95" s="4" t="n">
+      <c r="G95" s="4" t="n">
         <v>-2.5</v>
       </c>
-      <c r="G95" s="4" t="n">
+      <c r="H95" s="4" t="n">
         <v>-3.33</v>
       </c>
-      <c r="H95" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J95" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5492,33 +5813,36 @@
         <v>710</v>
       </c>
       <c r="D96" t="n">
+        <v/>
+      </c>
+      <c r="E96" t="n">
         <v>660</v>
       </c>
-      <c r="E96" t="n">
+      <c r="F96" t="n">
         <v>710</v>
       </c>
-      <c r="F96" s="4" t="n">
+      <c r="G96" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G96" s="4" t="n">
+      <c r="H96" s="4" t="n">
         <v>-7.04</v>
       </c>
-      <c r="H96" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J96" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5539,33 +5863,36 @@
         <v>2080</v>
       </c>
       <c r="D97" t="n">
+        <v/>
+      </c>
+      <c r="E97" t="n">
         <v>2120</v>
       </c>
-      <c r="E97" t="n">
+      <c r="F97" t="n">
         <v>2320</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="G97" s="4" t="n">
         <v>11.54</v>
       </c>
-      <c r="G97" s="4" t="n">
+      <c r="H97" s="4" t="n">
         <v>1.92</v>
       </c>
-      <c r="H97" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I97" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J97" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5586,33 +5913,36 @@
         <v>90</v>
       </c>
       <c r="D98" t="n">
+        <v/>
+      </c>
+      <c r="E98" t="n">
         <v>89</v>
       </c>
-      <c r="E98" t="n">
+      <c r="F98" t="n">
         <v>92</v>
       </c>
-      <c r="F98" s="4" t="n">
+      <c r="G98" s="4" t="n">
         <v>2.22</v>
       </c>
-      <c r="G98" s="4" t="n">
+      <c r="H98" s="4" t="n">
         <v>-1.11</v>
       </c>
-      <c r="H98" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I98" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J98" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5633,33 +5963,36 @@
         <v>85</v>
       </c>
       <c r="D99" t="n">
+        <v/>
+      </c>
+      <c r="E99" t="n">
         <v>83</v>
       </c>
-      <c r="E99" t="n">
+      <c r="F99" t="n">
         <v>90</v>
       </c>
-      <c r="F99" s="4" t="n">
+      <c r="G99" s="4" t="n">
         <v>5.88</v>
       </c>
-      <c r="G99" s="4" t="n">
+      <c r="H99" s="4" t="n">
         <v>-2.35</v>
       </c>
-      <c r="H99" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I99" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I99" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J99" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5680,33 +6013,36 @@
         <v>110</v>
       </c>
       <c r="D100" t="n">
+        <v/>
+      </c>
+      <c r="E100" t="n">
         <v>117</v>
       </c>
-      <c r="E100" t="n">
+      <c r="F100" t="n">
         <v>120</v>
       </c>
-      <c r="F100" s="4" t="n">
+      <c r="G100" s="4" t="n">
         <v>9.09</v>
       </c>
-      <c r="G100" s="4" t="n">
+      <c r="H100" s="4" t="n">
         <v>6.36</v>
       </c>
-      <c r="H100" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I100" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J100" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5727,33 +6063,36 @@
         <v>173</v>
       </c>
       <c r="D101" t="n">
+        <v/>
+      </c>
+      <c r="E101" t="n">
         <v>169</v>
       </c>
-      <c r="E101" t="n">
+      <c r="F101" t="n">
         <v>180</v>
       </c>
-      <c r="F101" s="4" t="n">
+      <c r="G101" s="4" t="n">
         <v>4.05</v>
       </c>
-      <c r="G101" s="4" t="n">
+      <c r="H101" s="4" t="n">
         <v>-2.31</v>
       </c>
-      <c r="H101" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I101" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J101" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5774,33 +6113,36 @@
         <v>575</v>
       </c>
       <c r="D102" t="n">
+        <v/>
+      </c>
+      <c r="E102" t="n">
         <v>570</v>
       </c>
-      <c r="E102" t="n">
+      <c r="F102" t="n">
         <v>580</v>
       </c>
-      <c r="F102" s="4" t="n">
+      <c r="G102" s="4" t="n">
         <v>0.87</v>
       </c>
-      <c r="G102" s="4" t="n">
+      <c r="H102" s="4" t="n">
         <v>-0.87</v>
       </c>
-      <c r="H102" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I102" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J102" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5821,33 +6163,36 @@
         <v>140</v>
       </c>
       <c r="D103" t="n">
+        <v/>
+      </c>
+      <c r="E103" t="n">
         <v>138</v>
       </c>
-      <c r="E103" t="n">
+      <c r="F103" t="n">
         <v>140</v>
       </c>
-      <c r="F103" s="4" t="n">
+      <c r="G103" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G103" s="4" t="n">
+      <c r="H103" s="4" t="n">
         <v>-1.43</v>
       </c>
-      <c r="H103" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J103" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5868,33 +6213,36 @@
         <v>1990</v>
       </c>
       <c r="D104" t="n">
+        <v/>
+      </c>
+      <c r="E104" t="n">
         <v>2020</v>
       </c>
-      <c r="E104" t="n">
+      <c r="F104" t="n">
         <v>2100</v>
       </c>
-      <c r="F104" s="4" t="n">
+      <c r="G104" s="4" t="n">
         <v>5.53</v>
       </c>
-      <c r="G104" s="4" t="n">
+      <c r="H104" s="4" t="n">
         <v>1.51</v>
       </c>
-      <c r="H104" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I104" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J104" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5915,33 +6263,36 @@
         <v>118</v>
       </c>
       <c r="D105" t="n">
+        <v/>
+      </c>
+      <c r="E105" t="n">
         <v>116</v>
       </c>
-      <c r="E105" t="n">
+      <c r="F105" t="n">
         <v>121</v>
       </c>
-      <c r="F105" s="4" t="n">
+      <c r="G105" s="4" t="n">
         <v>2.54</v>
       </c>
-      <c r="G105" s="4" t="n">
+      <c r="H105" s="4" t="n">
         <v>-1.69</v>
       </c>
-      <c r="H105" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I105" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J105" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5962,33 +6313,36 @@
         <v>366</v>
       </c>
       <c r="D106" t="n">
+        <v/>
+      </c>
+      <c r="E106" t="n">
         <v>360</v>
       </c>
-      <c r="E106" t="n">
+      <c r="F106" t="n">
         <v>364</v>
       </c>
-      <c r="F106" s="4" t="n">
+      <c r="G106" s="4" t="n">
         <v>-0.55</v>
       </c>
-      <c r="G106" s="4" t="n">
+      <c r="H106" s="4" t="n">
         <v>-1.64</v>
       </c>
-      <c r="H106" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J106" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6009,33 +6363,36 @@
         <v>131</v>
       </c>
       <c r="D107" t="n">
+        <v/>
+      </c>
+      <c r="E107" t="n">
         <v>130</v>
       </c>
-      <c r="E107" t="n">
+      <c r="F107" t="n">
         <v>132</v>
       </c>
-      <c r="F107" s="4" t="n">
+      <c r="G107" s="4" t="n">
         <v>0.76</v>
       </c>
-      <c r="G107" s="4" t="n">
+      <c r="H107" s="4" t="n">
         <v>-0.76</v>
       </c>
-      <c r="H107" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I107" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J107" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6056,33 +6413,36 @@
         <v>7325</v>
       </c>
       <c r="D108" t="n">
+        <v/>
+      </c>
+      <c r="E108" t="n">
         <v>7075</v>
       </c>
-      <c r="E108" t="n">
+      <c r="F108" t="n">
         <v>7475</v>
       </c>
-      <c r="F108" s="4" t="n">
+      <c r="G108" s="4" t="n">
         <v>2.05</v>
       </c>
-      <c r="G108" s="4" t="n">
+      <c r="H108" s="4" t="n">
         <v>-3.41</v>
       </c>
-      <c r="H108" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I108" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J108" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6103,33 +6463,36 @@
         <v>3760</v>
       </c>
       <c r="D109" t="n">
+        <v/>
+      </c>
+      <c r="E109" t="n">
         <v>3580</v>
       </c>
-      <c r="E109" t="n">
+      <c r="F109" t="n">
         <v>3760</v>
       </c>
-      <c r="F109" s="4" t="n">
+      <c r="G109" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G109" s="4" t="n">
+      <c r="H109" s="4" t="n">
         <v>-4.79</v>
       </c>
-      <c r="H109" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J109" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6150,33 +6513,36 @@
         <v>975</v>
       </c>
       <c r="D110" t="n">
+        <v/>
+      </c>
+      <c r="E110" t="n">
         <v>960</v>
       </c>
-      <c r="E110" t="n">
+      <c r="F110" t="n">
         <v>995</v>
       </c>
-      <c r="F110" s="4" t="n">
+      <c r="G110" s="4" t="n">
         <v>2.05</v>
       </c>
-      <c r="G110" s="4" t="n">
+      <c r="H110" s="4" t="n">
         <v>-1.54</v>
       </c>
-      <c r="H110" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I110" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J110" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6197,33 +6563,36 @@
         <v>264</v>
       </c>
       <c r="D111" t="n">
+        <v/>
+      </c>
+      <c r="E111" t="n">
         <v>264</v>
       </c>
-      <c r="E111" t="n">
+      <c r="F111" t="n">
         <v>268</v>
       </c>
-      <c r="F111" s="4" t="n">
+      <c r="G111" s="4" t="n">
         <v>1.52</v>
       </c>
-      <c r="G111" s="4" t="n">
+      <c r="H111" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H111" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I111" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J111" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6244,33 +6613,36 @@
         <v>121</v>
       </c>
       <c r="D112" t="n">
+        <v/>
+      </c>
+      <c r="E112" t="n">
         <v>123</v>
       </c>
-      <c r="E112" t="n">
+      <c r="F112" t="n">
         <v>126</v>
       </c>
-      <c r="F112" s="4" t="n">
+      <c r="G112" s="4" t="n">
         <v>4.13</v>
       </c>
-      <c r="G112" s="4" t="n">
+      <c r="H112" s="4" t="n">
         <v>1.65</v>
       </c>
-      <c r="H112" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I112" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J112" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6291,33 +6663,36 @@
         <v>865</v>
       </c>
       <c r="D113" t="n">
+        <v/>
+      </c>
+      <c r="E113" t="n">
         <v>885</v>
       </c>
-      <c r="E113" t="n">
+      <c r="F113" t="n">
         <v>895</v>
       </c>
-      <c r="F113" s="4" t="n">
+      <c r="G113" s="4" t="n">
         <v>3.47</v>
       </c>
-      <c r="G113" s="4" t="n">
+      <c r="H113" s="4" t="n">
         <v>2.31</v>
       </c>
-      <c r="H113" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I113" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="J113" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6338,33 +6713,36 @@
         <v>540</v>
       </c>
       <c r="D114" t="n">
+        <v/>
+      </c>
+      <c r="E114" t="n">
         <v>525</v>
       </c>
-      <c r="E114" t="n">
+      <c r="F114" t="n">
         <v>545</v>
       </c>
-      <c r="F114" s="4" t="n">
+      <c r="G114" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="G114" s="4" t="n">
+      <c r="H114" s="4" t="n">
         <v>-2.78</v>
       </c>
-      <c r="H114" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I114" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J114" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6385,33 +6763,36 @@
         <v>244</v>
       </c>
       <c r="D115" t="n">
+        <v/>
+      </c>
+      <c r="E115" t="n">
         <v>234</v>
       </c>
-      <c r="E115" t="n">
+      <c r="F115" t="n">
         <v>246</v>
       </c>
-      <c r="F115" s="4" t="n">
+      <c r="G115" s="4" t="n">
         <v>0.82</v>
       </c>
-      <c r="G115" s="4" t="n">
+      <c r="H115" s="4" t="n">
         <v>-4.1</v>
       </c>
-      <c r="H115" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I115" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I115" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J115" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6432,33 +6813,36 @@
         <v>91</v>
       </c>
       <c r="D116" t="n">
+        <v/>
+      </c>
+      <c r="E116" t="n">
         <v>90</v>
       </c>
-      <c r="E116" t="n">
+      <c r="F116" t="n">
         <v>93</v>
       </c>
-      <c r="F116" s="4" t="n">
+      <c r="G116" s="4" t="n">
         <v>2.2</v>
       </c>
-      <c r="G116" s="4" t="n">
+      <c r="H116" s="4" t="n">
         <v>-1.1</v>
       </c>
-      <c r="H116" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I116" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J116" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>

--- a/data/performance/daily/signal_list_2026-06-22.xlsx
+++ b/data/performance/daily/signal_list_2026-06-22.xlsx
@@ -559,7 +559,7 @@
         <v>1710</v>
       </c>
       <c r="D5" t="n">
-        <v/>
+        <v>1553.99</v>
       </c>
       <c r="E5" t="n">
         <v>1720</v>
@@ -609,7 +609,7 @@
         <v>16625</v>
       </c>
       <c r="D6" t="n">
-        <v/>
+        <v>15865</v>
       </c>
       <c r="E6" t="n">
         <v>17000</v>
@@ -659,7 +659,7 @@
         <v>1510</v>
       </c>
       <c r="D7" t="n">
-        <v/>
+        <v>1500.07</v>
       </c>
       <c r="E7" t="n">
         <v>1515</v>
@@ -709,7 +709,7 @@
         <v>5879</v>
       </c>
       <c r="D8" t="n">
-        <v/>
+        <v>6000</v>
       </c>
       <c r="E8" t="n">
         <v>6050</v>
@@ -759,7 +759,7 @@
         <v>955</v>
       </c>
       <c r="D9" t="n">
-        <v/>
+        <v>955</v>
       </c>
       <c r="E9" t="n">
         <v>955</v>
@@ -809,7 +809,7 @@
         <v>1830</v>
       </c>
       <c r="D10" t="n">
-        <v/>
+        <v>1635.97</v>
       </c>
       <c r="E10" t="n">
         <v>1840</v>
@@ -859,7 +859,7 @@
         <v>705</v>
       </c>
       <c r="D11" t="n">
-        <v/>
+        <v>705</v>
       </c>
       <c r="E11" t="n">
         <v>700</v>
@@ -909,7 +909,7 @@
         <v>7800</v>
       </c>
       <c r="D12" t="n">
-        <v/>
+        <v>8125</v>
       </c>
       <c r="E12" t="n">
         <v>7900</v>
@@ -959,7 +959,7 @@
         <v>460</v>
       </c>
       <c r="D13" t="n">
-        <v/>
+        <v>462</v>
       </c>
       <c r="E13" t="n">
         <v>474</v>
@@ -1009,7 +1009,7 @@
         <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v/>
+        <v>103</v>
       </c>
       <c r="E14" t="n">
         <v>96</v>
@@ -1059,7 +1059,7 @@
         <v>710</v>
       </c>
       <c r="D15" t="n">
-        <v/>
+        <v>705</v>
       </c>
       <c r="E15" t="n">
         <v>660</v>
@@ -1109,7 +1109,7 @@
         <v>575</v>
       </c>
       <c r="D16" t="n">
-        <v/>
+        <v>575</v>
       </c>
       <c r="E16" t="n">
         <v>570</v>
@@ -1263,7 +1263,7 @@
         <v>910</v>
       </c>
       <c r="D5" t="n">
-        <v/>
+        <v>950</v>
       </c>
       <c r="E5" t="n">
         <v>865</v>
@@ -1313,7 +1313,7 @@
         <v>408.3</v>
       </c>
       <c r="D6" t="n">
-        <v/>
+        <v>420</v>
       </c>
       <c r="E6" t="n">
         <v>398</v>
@@ -1363,7 +1363,7 @@
         <v>165</v>
       </c>
       <c r="D7" t="n">
-        <v/>
+        <v>167</v>
       </c>
       <c r="E7" t="n">
         <v>162</v>
@@ -1413,7 +1413,7 @@
         <v>6300</v>
       </c>
       <c r="D8" t="n">
-        <v/>
+        <v>6400</v>
       </c>
       <c r="E8" t="n">
         <v>6200</v>
@@ -1463,7 +1463,7 @@
         <v>145</v>
       </c>
       <c r="D9" t="n">
-        <v/>
+        <v>149</v>
       </c>
       <c r="E9" t="n">
         <v>139</v>
@@ -1513,7 +1513,7 @@
         <v>1675</v>
       </c>
       <c r="D10" t="n">
-        <v/>
+        <v>1514.49</v>
       </c>
       <c r="E10" t="n">
         <v>1670</v>
@@ -1563,7 +1563,7 @@
         <v>314</v>
       </c>
       <c r="D11" t="n">
-        <v/>
+        <v>346</v>
       </c>
       <c r="E11" t="n">
         <v>298</v>
@@ -1613,7 +1613,7 @@
         <v>660</v>
       </c>
       <c r="D12" t="n">
-        <v/>
+        <v>660</v>
       </c>
       <c r="E12" t="n">
         <v>635</v>
@@ -1663,7 +1663,7 @@
         <v>1280</v>
       </c>
       <c r="D13" t="n">
-        <v/>
+        <v>1280</v>
       </c>
       <c r="E13" t="n">
         <v>1210</v>
@@ -1713,7 +1713,7 @@
         <v>870</v>
       </c>
       <c r="D14" t="n">
-        <v/>
+        <v>880</v>
       </c>
       <c r="E14" t="n">
         <v>825</v>
@@ -1763,7 +1763,7 @@
         <v>11000</v>
       </c>
       <c r="D15" t="n">
-        <v/>
+        <v>11000</v>
       </c>
       <c r="E15" t="n">
         <v>11675</v>
@@ -1813,7 +1813,7 @@
         <v>2380</v>
       </c>
       <c r="D16" t="n">
-        <v/>
+        <v>2240.55</v>
       </c>
       <c r="E16" t="n">
         <v>2400</v>
@@ -1863,7 +1863,7 @@
         <v>366</v>
       </c>
       <c r="D17" t="n">
-        <v/>
+        <v>319.32</v>
       </c>
       <c r="E17" t="n">
         <v>362</v>
@@ -1913,7 +1913,7 @@
         <v>1710</v>
       </c>
       <c r="D18" t="n">
-        <v/>
+        <v>1553.99</v>
       </c>
       <c r="E18" t="n">
         <v>1720</v>
@@ -1963,7 +1963,7 @@
         <v>290</v>
       </c>
       <c r="D19" t="n">
-        <v/>
+        <v>286</v>
       </c>
       <c r="E19" t="n">
         <v>284</v>
@@ -2013,7 +2013,7 @@
         <v>72</v>
       </c>
       <c r="D20" t="n">
-        <v/>
+        <v>72</v>
       </c>
       <c r="E20" t="n">
         <v>71</v>
@@ -2063,7 +2063,7 @@
         <v>850</v>
       </c>
       <c r="D21" t="n">
-        <v/>
+        <v>865</v>
       </c>
       <c r="E21" t="n">
         <v>870</v>
@@ -2113,7 +2113,7 @@
         <v>16625</v>
       </c>
       <c r="D22" t="n">
-        <v/>
+        <v>15865</v>
       </c>
       <c r="E22" t="n">
         <v>17000</v>
@@ -2163,7 +2163,7 @@
         <v>1200</v>
       </c>
       <c r="D23" t="n">
-        <v/>
+        <v>1195</v>
       </c>
       <c r="E23" t="n">
         <v>1175</v>
@@ -2213,7 +2213,7 @@
         <v>270</v>
       </c>
       <c r="D24" t="n">
-        <v/>
+        <v>280</v>
       </c>
       <c r="E24" t="n">
         <v>262</v>
@@ -2263,7 +2263,7 @@
         <v>825</v>
       </c>
       <c r="D25" t="n">
-        <v/>
+        <v>825</v>
       </c>
       <c r="E25" t="n">
         <v>860</v>
@@ -2313,7 +2313,7 @@
         <v>75</v>
       </c>
       <c r="D26" t="n">
-        <v/>
+        <v>82</v>
       </c>
       <c r="E26" t="n">
         <v>80</v>
@@ -2363,7 +2363,7 @@
         <v>6725</v>
       </c>
       <c r="D27" t="n">
-        <v/>
+        <v>6538.15</v>
       </c>
       <c r="E27" t="n">
         <v>6800</v>
@@ -2413,7 +2413,7 @@
         <v>700</v>
       </c>
       <c r="D28" t="n">
-        <v/>
+        <v>631.71</v>
       </c>
       <c r="E28" t="n">
         <v>670</v>
@@ -2463,7 +2463,7 @@
         <v>470</v>
       </c>
       <c r="D29" t="n">
-        <v/>
+        <v>470</v>
       </c>
       <c r="E29" t="n">
         <v>446</v>
@@ -2513,7 +2513,7 @@
         <v>1340</v>
       </c>
       <c r="D30" t="n">
-        <v/>
+        <v>1340</v>
       </c>
       <c r="E30" t="n">
         <v>1355</v>
@@ -2563,7 +2563,7 @@
         <v>286</v>
       </c>
       <c r="D31" t="n">
-        <v/>
+        <v>273.1</v>
       </c>
       <c r="E31" t="n">
         <v>286</v>
@@ -2613,7 +2613,7 @@
         <v>795</v>
       </c>
       <c r="D32" t="n">
-        <v/>
+        <v>800</v>
       </c>
       <c r="E32" t="n">
         <v>795</v>
@@ -2663,7 +2663,7 @@
         <v>2620</v>
       </c>
       <c r="D33" t="n">
-        <v/>
+        <v>2620</v>
       </c>
       <c r="E33" t="n">
         <v>2610</v>
@@ -2713,7 +2713,7 @@
         <v>2930</v>
       </c>
       <c r="D34" t="n">
-        <v/>
+        <v>2985.49</v>
       </c>
       <c r="E34" t="n">
         <v>2980</v>
@@ -2763,7 +2763,7 @@
         <v>1600</v>
       </c>
       <c r="D35" t="n">
-        <v/>
+        <v>1615</v>
       </c>
       <c r="E35" t="n">
         <v>1575</v>
@@ -2813,7 +2813,7 @@
         <v>21825</v>
       </c>
       <c r="D36" t="n">
-        <v/>
+        <v>20907.55</v>
       </c>
       <c r="E36" t="n">
         <v>22025</v>
@@ -2863,7 +2863,7 @@
         <v>52</v>
       </c>
       <c r="D37" t="n">
-        <v/>
+        <v>50</v>
       </c>
       <c r="E37" t="n">
         <v>52</v>
@@ -2913,7 +2913,7 @@
         <v>1990</v>
       </c>
       <c r="D38" t="n">
-        <v/>
+        <v>1950</v>
       </c>
       <c r="E38" t="n">
         <v>1865</v>
@@ -2963,7 +2963,7 @@
         <v>1830</v>
       </c>
       <c r="D39" t="n">
-        <v/>
+        <v>1635.97</v>
       </c>
       <c r="E39" t="n">
         <v>1840</v>
@@ -3013,7 +3013,7 @@
         <v>94</v>
       </c>
       <c r="D40" t="n">
-        <v/>
+        <v>103</v>
       </c>
       <c r="E40" t="n">
         <v>99</v>
@@ -3063,7 +3063,7 @@
         <v>162</v>
       </c>
       <c r="D41" t="n">
-        <v/>
+        <v>162</v>
       </c>
       <c r="E41" t="n">
         <v>160</v>
@@ -3113,7 +3113,7 @@
         <v>2150</v>
       </c>
       <c r="D42" t="n">
-        <v/>
+        <v>2150</v>
       </c>
       <c r="E42" t="n">
         <v>1935</v>
@@ -3163,7 +3163,7 @@
         <v>71</v>
       </c>
       <c r="D43" t="n">
-        <v/>
+        <v>72</v>
       </c>
       <c r="E43" t="n">
         <v>71</v>
@@ -3213,7 +3213,7 @@
         <v>1515</v>
       </c>
       <c r="D44" t="n">
-        <v/>
+        <v>1520</v>
       </c>
       <c r="E44" t="n">
         <v>1515</v>
@@ -3263,7 +3263,7 @@
         <v>665</v>
       </c>
       <c r="D45" t="n">
-        <v/>
+        <v>606.3200000000001</v>
       </c>
       <c r="E45" t="n">
         <v>665</v>
@@ -3313,7 +3313,7 @@
         <v>3490</v>
       </c>
       <c r="D46" t="n">
-        <v/>
+        <v>3416.8</v>
       </c>
       <c r="E46" t="n">
         <v>3730</v>
@@ -3363,7 +3363,7 @@
         <v>595</v>
       </c>
       <c r="D47" t="n">
-        <v/>
+        <v>560</v>
       </c>
       <c r="E47" t="n">
         <v>555</v>
@@ -3413,7 +3413,7 @@
         <v>5975</v>
       </c>
       <c r="D48" t="n">
-        <v/>
+        <v>5991.37</v>
       </c>
       <c r="E48" t="n">
         <v>6000</v>
@@ -3463,7 +3463,7 @@
         <v>372</v>
       </c>
       <c r="D49" t="n">
-        <v/>
+        <v>374</v>
       </c>
       <c r="E49" t="n">
         <v>370</v>
@@ -3513,7 +3513,7 @@
         <v>555</v>
       </c>
       <c r="D50" t="n">
-        <v/>
+        <v>564.0599999999999</v>
       </c>
       <c r="E50" t="n">
         <v>560</v>
@@ -3563,7 +3563,7 @@
         <v>168</v>
       </c>
       <c r="D51" t="n">
-        <v/>
+        <v>171</v>
       </c>
       <c r="E51" t="n">
         <v>170</v>
@@ -3613,7 +3613,7 @@
         <v>1685</v>
       </c>
       <c r="D52" t="n">
-        <v/>
+        <v>1725</v>
       </c>
       <c r="E52" t="n">
         <v>1690</v>
@@ -3663,7 +3663,7 @@
         <v>1680</v>
       </c>
       <c r="D53" t="n">
-        <v/>
+        <v>1680</v>
       </c>
       <c r="E53" t="n">
         <v>1665</v>
@@ -3713,7 +3713,7 @@
         <v>1345</v>
       </c>
       <c r="D54" t="n">
-        <v/>
+        <v>1400</v>
       </c>
       <c r="E54" t="n">
         <v>1400</v>
@@ -3763,7 +3763,7 @@
         <v>7800</v>
       </c>
       <c r="D55" t="n">
-        <v/>
+        <v>8125</v>
       </c>
       <c r="E55" t="n">
         <v>7900</v>
@@ -3813,7 +3813,7 @@
         <v>189</v>
       </c>
       <c r="D56" t="n">
-        <v/>
+        <v>187</v>
       </c>
       <c r="E56" t="n">
         <v>187</v>
@@ -3863,7 +3863,7 @@
         <v>430</v>
       </c>
       <c r="D57" t="n">
-        <v/>
+        <v>430</v>
       </c>
       <c r="E57" t="n">
         <v>432</v>
@@ -3913,7 +3913,7 @@
         <v>630</v>
       </c>
       <c r="D58" t="n">
-        <v/>
+        <v>635</v>
       </c>
       <c r="E58" t="n">
         <v>580</v>
@@ -3963,7 +3963,7 @@
         <v>1163.31</v>
       </c>
       <c r="D59" t="n">
-        <v/>
+        <v>1150</v>
       </c>
       <c r="E59" t="n">
         <v>1185</v>
@@ -4013,7 +4013,7 @@
         <v>172</v>
       </c>
       <c r="D60" t="n">
-        <v/>
+        <v>178</v>
       </c>
       <c r="E60" t="n">
         <v>172</v>
@@ -4063,7 +4063,7 @@
         <v>85</v>
       </c>
       <c r="D61" t="n">
-        <v/>
+        <v>85</v>
       </c>
       <c r="E61" t="n">
         <v>85</v>
@@ -4113,7 +4113,7 @@
         <v>160</v>
       </c>
       <c r="D62" t="n">
-        <v/>
+        <v>160</v>
       </c>
       <c r="E62" t="n">
         <v>160</v>
@@ -4163,7 +4163,7 @@
         <v>254</v>
       </c>
       <c r="D63" t="n">
-        <v/>
+        <v>254</v>
       </c>
       <c r="E63" t="n">
         <v>256</v>
@@ -4213,7 +4213,7 @@
         <v>13800</v>
       </c>
       <c r="D64" t="n">
-        <v/>
+        <v>13800</v>
       </c>
       <c r="E64" t="n">
         <v>13975</v>
@@ -4263,7 +4263,7 @@
         <v>100</v>
       </c>
       <c r="D65" t="n">
-        <v/>
+        <v>101</v>
       </c>
       <c r="E65" t="n">
         <v>104</v>
@@ -4313,7 +4313,7 @@
         <v>65</v>
       </c>
       <c r="D66" t="n">
-        <v/>
+        <v>65</v>
       </c>
       <c r="E66" t="n">
         <v>64</v>
@@ -4363,7 +4363,7 @@
         <v>134</v>
       </c>
       <c r="D67" t="n">
-        <v/>
+        <v>134.47</v>
       </c>
       <c r="E67" t="n">
         <v>150</v>
@@ -4413,7 +4413,7 @@
         <v>1555</v>
       </c>
       <c r="D68" t="n">
-        <v/>
+        <v>1600</v>
       </c>
       <c r="E68" t="n">
         <v>1500</v>
@@ -4463,7 +4463,7 @@
         <v>1300</v>
       </c>
       <c r="D69" t="n">
-        <v/>
+        <v>1250</v>
       </c>
       <c r="E69" t="n">
         <v>1335</v>
@@ -4513,7 +4513,7 @@
         <v>68</v>
       </c>
       <c r="D70" t="n">
-        <v/>
+        <v>68</v>
       </c>
       <c r="E70" t="n">
         <v>70</v>
@@ -4563,7 +4563,7 @@
         <v>151</v>
       </c>
       <c r="D71" t="n">
-        <v/>
+        <v>151</v>
       </c>
       <c r="E71" t="n">
         <v>147</v>
@@ -4613,7 +4613,7 @@
         <v>1775</v>
       </c>
       <c r="D72" t="n">
-        <v/>
+        <v>1980</v>
       </c>
       <c r="E72" t="n">
         <v>1850</v>
@@ -4663,7 +4663,7 @@
         <v>494</v>
       </c>
       <c r="D73" t="n">
-        <v/>
+        <v>494</v>
       </c>
       <c r="E73" t="n">
         <v>488</v>
@@ -4713,7 +4713,7 @@
         <v>133</v>
       </c>
       <c r="D74" t="n">
-        <v/>
+        <v>133</v>
       </c>
       <c r="E74" t="n">
         <v>134</v>
@@ -4763,7 +4763,7 @@
         <v>1505</v>
       </c>
       <c r="D75" t="n">
-        <v/>
+        <v>1505</v>
       </c>
       <c r="E75" t="n">
         <v>1355</v>
@@ -4813,7 +4813,7 @@
         <v>94</v>
       </c>
       <c r="D76" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="E76" t="n">
         <v>92</v>
@@ -4863,7 +4863,7 @@
         <v>590</v>
       </c>
       <c r="D77" t="n">
-        <v/>
+        <v>590</v>
       </c>
       <c r="E77" t="n">
         <v>570</v>
@@ -4913,7 +4913,7 @@
         <v>192</v>
       </c>
       <c r="D78" t="n">
-        <v/>
+        <v>190</v>
       </c>
       <c r="E78" t="n">
         <v>182</v>
@@ -4963,7 +4963,7 @@
         <v>460</v>
       </c>
       <c r="D79" t="n">
-        <v/>
+        <v>462</v>
       </c>
       <c r="E79" t="n">
         <v>474</v>
@@ -5013,7 +5013,7 @@
         <v>6450</v>
       </c>
       <c r="D80" t="n">
-        <v/>
+        <v>6600</v>
       </c>
       <c r="E80" t="n">
         <v>6225</v>
@@ -5063,7 +5063,7 @@
         <v>346</v>
       </c>
       <c r="D81" t="n">
-        <v/>
+        <v>346</v>
       </c>
       <c r="E81" t="n">
         <v>352</v>
@@ -5113,7 +5113,7 @@
         <v>2030</v>
       </c>
       <c r="D82" t="n">
-        <v/>
+        <v>2132.99</v>
       </c>
       <c r="E82" t="n">
         <v>2070</v>
@@ -5163,7 +5163,7 @@
         <v>745</v>
       </c>
       <c r="D83" t="n">
-        <v/>
+        <v>745</v>
       </c>
       <c r="E83" t="n">
         <v>720</v>
@@ -5213,7 +5213,7 @@
         <v>210</v>
       </c>
       <c r="D84" t="n">
-        <v/>
+        <v>210</v>
       </c>
       <c r="E84" t="n">
         <v>212</v>
@@ -5263,7 +5263,7 @@
         <v>187</v>
       </c>
       <c r="D85" t="n">
-        <v/>
+        <v>189</v>
       </c>
       <c r="E85" t="n">
         <v>183</v>
@@ -5313,7 +5313,7 @@
         <v>67</v>
       </c>
       <c r="D86" t="n">
-        <v/>
+        <v>66</v>
       </c>
       <c r="E86" t="n">
         <v>65</v>
@@ -5363,7 +5363,7 @@
         <v>139</v>
       </c>
       <c r="D87" t="n">
-        <v/>
+        <v>136.27</v>
       </c>
       <c r="E87" t="n">
         <v>137</v>
@@ -5413,7 +5413,7 @@
         <v>98</v>
       </c>
       <c r="D88" t="n">
-        <v/>
+        <v>101</v>
       </c>
       <c r="E88" t="n">
         <v>98</v>
@@ -5463,7 +5463,7 @@
         <v>585</v>
       </c>
       <c r="D89" t="n">
-        <v/>
+        <v>585.16</v>
       </c>
       <c r="E89" t="n">
         <v>555</v>
@@ -5513,7 +5513,7 @@
         <v>270</v>
       </c>
       <c r="D90" t="n">
-        <v/>
+        <v>270</v>
       </c>
       <c r="E90" t="n">
         <v>260</v>
@@ -5563,7 +5563,7 @@
         <v>650</v>
       </c>
       <c r="D91" t="n">
-        <v/>
+        <v>650</v>
       </c>
       <c r="E91" t="n">
         <v>660</v>
@@ -5613,7 +5613,7 @@
         <v>116</v>
       </c>
       <c r="D92" t="n">
-        <v/>
+        <v>120</v>
       </c>
       <c r="E92" t="n">
         <v>117</v>
@@ -5663,7 +5663,7 @@
         <v>59</v>
       </c>
       <c r="D93" t="n">
-        <v/>
+        <v>59</v>
       </c>
       <c r="E93" t="n">
         <v>59</v>
@@ -5713,7 +5713,7 @@
         <v>101</v>
       </c>
       <c r="D94" t="n">
-        <v/>
+        <v>103</v>
       </c>
       <c r="E94" t="n">
         <v>96</v>
@@ -5763,7 +5763,7 @@
         <v>240</v>
       </c>
       <c r="D95" t="n">
-        <v/>
+        <v>234</v>
       </c>
       <c r="E95" t="n">
         <v>232</v>
@@ -5813,7 +5813,7 @@
         <v>710</v>
       </c>
       <c r="D96" t="n">
-        <v/>
+        <v>705</v>
       </c>
       <c r="E96" t="n">
         <v>660</v>
@@ -5863,7 +5863,7 @@
         <v>2080</v>
       </c>
       <c r="D97" t="n">
-        <v/>
+        <v>2100</v>
       </c>
       <c r="E97" t="n">
         <v>2120</v>
@@ -5913,7 +5913,7 @@
         <v>90</v>
       </c>
       <c r="D98" t="n">
-        <v/>
+        <v>88.91</v>
       </c>
       <c r="E98" t="n">
         <v>89</v>
@@ -5963,7 +5963,7 @@
         <v>85</v>
       </c>
       <c r="D99" t="n">
-        <v/>
+        <v>85</v>
       </c>
       <c r="E99" t="n">
         <v>83</v>
@@ -6013,7 +6013,7 @@
         <v>110</v>
       </c>
       <c r="D100" t="n">
-        <v/>
+        <v>107.86</v>
       </c>
       <c r="E100" t="n">
         <v>117</v>
@@ -6063,7 +6063,7 @@
         <v>173</v>
       </c>
       <c r="D101" t="n">
-        <v/>
+        <v>170</v>
       </c>
       <c r="E101" t="n">
         <v>169</v>
@@ -6113,7 +6113,7 @@
         <v>575</v>
       </c>
       <c r="D102" t="n">
-        <v/>
+        <v>575</v>
       </c>
       <c r="E102" t="n">
         <v>570</v>
@@ -6163,7 +6163,7 @@
         <v>140</v>
       </c>
       <c r="D103" t="n">
-        <v/>
+        <v>140</v>
       </c>
       <c r="E103" t="n">
         <v>138</v>
@@ -6213,7 +6213,7 @@
         <v>1990</v>
       </c>
       <c r="D104" t="n">
-        <v/>
+        <v>1990</v>
       </c>
       <c r="E104" t="n">
         <v>2020</v>
@@ -6263,7 +6263,7 @@
         <v>118</v>
       </c>
       <c r="D105" t="n">
-        <v/>
+        <v>118</v>
       </c>
       <c r="E105" t="n">
         <v>116</v>
@@ -6313,7 +6313,7 @@
         <v>366</v>
       </c>
       <c r="D106" t="n">
-        <v/>
+        <v>364</v>
       </c>
       <c r="E106" t="n">
         <v>360</v>
@@ -6363,7 +6363,7 @@
         <v>131</v>
       </c>
       <c r="D107" t="n">
-        <v/>
+        <v>131</v>
       </c>
       <c r="E107" t="n">
         <v>130</v>
@@ -6413,7 +6413,7 @@
         <v>7325</v>
       </c>
       <c r="D108" t="n">
-        <v/>
+        <v>7475</v>
       </c>
       <c r="E108" t="n">
         <v>7075</v>
@@ -6463,7 +6463,7 @@
         <v>3760</v>
       </c>
       <c r="D109" t="n">
-        <v/>
+        <v>3760</v>
       </c>
       <c r="E109" t="n">
         <v>3580</v>
@@ -6513,7 +6513,7 @@
         <v>975</v>
       </c>
       <c r="D110" t="n">
-        <v/>
+        <v>990.26</v>
       </c>
       <c r="E110" t="n">
         <v>960</v>
@@ -6563,7 +6563,7 @@
         <v>264</v>
       </c>
       <c r="D111" t="n">
-        <v/>
+        <v>268</v>
       </c>
       <c r="E111" t="n">
         <v>264</v>
@@ -6613,7 +6613,7 @@
         <v>121</v>
       </c>
       <c r="D112" t="n">
-        <v/>
+        <v>123</v>
       </c>
       <c r="E112" t="n">
         <v>123</v>
@@ -6663,7 +6663,7 @@
         <v>865</v>
       </c>
       <c r="D113" t="n">
-        <v/>
+        <v>810.8099999999999</v>
       </c>
       <c r="E113" t="n">
         <v>885</v>
@@ -6713,7 +6713,7 @@
         <v>540</v>
       </c>
       <c r="D114" t="n">
-        <v/>
+        <v>545</v>
       </c>
       <c r="E114" t="n">
         <v>525</v>
@@ -6763,7 +6763,7 @@
         <v>244</v>
       </c>
       <c r="D115" t="n">
-        <v/>
+        <v>246</v>
       </c>
       <c r="E115" t="n">
         <v>234</v>
@@ -6813,7 +6813,7 @@
         <v>91</v>
       </c>
       <c r="D116" t="n">
-        <v/>
+        <v>93</v>
       </c>
       <c r="E116" t="n">
         <v>90</v>
